--- a/items_data.xlsx
+++ b/items_data.xlsx
@@ -1,27 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlohakare\Desktop\BillCalculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BillCalculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F95D6DC-C346-42C5-9405-09F76145FB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63139AF-3A66-4F97-9228-F3DF8FF82E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
     <sheet name="BoxSize" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$D$200</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="101">
   <si>
     <t>Item Name</t>
   </si>
@@ -35,36 +38,311 @@
     <t>Discount</t>
   </si>
   <si>
-    <t>MCD No 1</t>
-  </si>
-  <si>
-    <t>750 ml</t>
-  </si>
-  <si>
-    <t>375 ml</t>
-  </si>
-  <si>
-    <t>180 ml</t>
-  </si>
-  <si>
-    <t>90 ml</t>
-  </si>
-  <si>
-    <t>Imperial Blue</t>
-  </si>
-  <si>
-    <t>Royal Stag</t>
-  </si>
-  <si>
     <t>NoOfBottles</t>
+  </si>
+  <si>
+    <t>100 PIPER WHISKY</t>
+  </si>
+  <si>
+    <t>100 PIPERS 12 YEARS SCOTCH WHISKY</t>
+  </si>
+  <si>
+    <t>100 PIPERS SCOTCH MALT WHISKY</t>
+  </si>
+  <si>
+    <t>ABSOLUT CITRON VODKA</t>
+  </si>
+  <si>
+    <t>ABSOLUT MANDRIN VODKA</t>
+  </si>
+  <si>
+    <t>ABSOLUT RASPBERRI VODKA</t>
+  </si>
+  <si>
+    <t>ABSOLUTE VODKA PLAIN</t>
+  </si>
+  <si>
+    <t>AFTER DARK BLUE WHISKY</t>
+  </si>
+  <si>
+    <t>ALL SEASONS DOUBLE RESERVE WHISKY</t>
+  </si>
+  <si>
+    <t>ANTIQUITY BLUE PR.WHISKY</t>
+  </si>
+  <si>
+    <t>BALLANTINES FINEST SCOTCH WHISKYY</t>
+  </si>
+  <si>
+    <t>BLACK &amp; WHITE SCOTCH WHISKY</t>
+  </si>
+  <si>
+    <t>BLACK DOG CENT.</t>
+  </si>
+  <si>
+    <t>BLACK DOG SCOTCH WHISKY</t>
+  </si>
+  <si>
+    <t>BLENDER PRIDE RESERVE WHISKY</t>
+  </si>
+  <si>
+    <t>BLENDERS PRIDE FOUR ELEMENTS WHISKY</t>
+  </si>
+  <si>
+    <t>BLENDERS PRIDE WHY.</t>
+  </si>
+  <si>
+    <t>Dram Bell 5 YO</t>
+  </si>
+  <si>
+    <t>Dram Bell Blended</t>
+  </si>
+  <si>
+    <t>DSP BLACK DELUX WHISKY 2LTR</t>
+  </si>
+  <si>
+    <t>DSP BLACK DELUX WHY.</t>
+  </si>
+  <si>
+    <t>DSP BLACK WHISKY PET</t>
+  </si>
+  <si>
+    <t>GIN SOAK PREMIUM DRY GIN</t>
+  </si>
+  <si>
+    <t>GLACIR PREMIUM VODKA</t>
+  </si>
+  <si>
+    <t>GRAND MASTER CRANBERRY VODKA</t>
+  </si>
+  <si>
+    <t>GRAND MASTER MELON VODKA</t>
+  </si>
+  <si>
+    <t>GRAND MASTER MELON(48*180ML)</t>
+  </si>
+  <si>
+    <t>GREEN LABEL S.G. WHISKY</t>
+  </si>
+  <si>
+    <t>ICONIQ WHITE WHISKY</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUE WHY.</t>
+  </si>
+  <si>
+    <t>J&amp;B RARE SCOTCH WHY.</t>
+  </si>
+  <si>
+    <t>J.W. BLACK LABLE WHISKY</t>
+  </si>
+  <si>
+    <t>J.W.RED LABEL SCOTCH WHISKY</t>
+  </si>
+  <si>
+    <t>JACK DANIEL HONEY FLO</t>
+  </si>
+  <si>
+    <t>JACK DANIEL No7 TENNESSEE WHY</t>
+  </si>
+  <si>
+    <t>JACK DANIEL TENNESSEE APPLE</t>
+  </si>
+  <si>
+    <t>JACK DENIEL FIRE WHISKY</t>
+  </si>
+  <si>
+    <t>JW BLONDE SCOTCH WHISKY</t>
+  </si>
+  <si>
+    <t>MAGIC MOMENTS APPLE VODKA</t>
+  </si>
+  <si>
+    <t>MAGIC MOMENTS GRAIN VODKA</t>
+  </si>
+  <si>
+    <t>MAGIC MOMENTS JAMUN SPICY MINT VODKA (PET)</t>
+  </si>
+  <si>
+    <t>MAGIC MOMENTS JAMUN VODKA</t>
+  </si>
+  <si>
+    <t>MAGIC MOMENTS ORANGE VODKA</t>
+  </si>
+  <si>
+    <t>MCD CELEBRATION RUM XXX</t>
+  </si>
+  <si>
+    <t>MCD NO.1 RESERVE WHY.</t>
+  </si>
+  <si>
+    <t>OAKSMITH GOLD (PEET)</t>
+  </si>
+  <si>
+    <t>OAKSMITH GOLD WHISKY</t>
+  </si>
+  <si>
+    <t>OAKSMITH INT (PEET)</t>
+  </si>
+  <si>
+    <t>OAKSMITH WHISKY</t>
+  </si>
+  <si>
+    <t>OFFICER"CHOICE BLUE WHISKY</t>
+  </si>
+  <si>
+    <t>ROMONOV VODKA</t>
+  </si>
+  <si>
+    <t>ROYAL CHALLANGE WHY</t>
+  </si>
+  <si>
+    <t>ROYAL CHALLENGE WHY PET</t>
+  </si>
+  <si>
+    <t>ROYAL GREEN SUPREME WHISKY</t>
+  </si>
+  <si>
+    <t>ROYAL RANTHAMBARE RESERVE  WHISKY</t>
+  </si>
+  <si>
+    <t>ROYAL STAG DOUBLE DARK PEATY WHISKY</t>
+  </si>
+  <si>
+    <t>ROYAL STAG WHY</t>
+  </si>
+  <si>
+    <t>ROYAL STAGE BARREL SELECT</t>
+  </si>
+  <si>
+    <t>SMIRNOFF GREEN APPLE T.VODKA</t>
+  </si>
+  <si>
+    <t>SMIRNOFF MINTY JAMUN TRIPLE DISTILLED FLAVOURED VODKA</t>
+  </si>
+  <si>
+    <t>SMIRNOFF MIRCHI MANGO TRIPLE DISTILLED FLAVOURED VODKA</t>
+  </si>
+  <si>
+    <t>SMIRNOFF VOD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMIRNOFF ZESTY LIME TRIPLE DISTILLED FLAVOURED VODKA </t>
+  </si>
+  <si>
+    <t>STERLING RESERVE B7 BLENDED WHISKY</t>
+  </si>
+  <si>
+    <t>AMSTEL STRONG BEER</t>
+  </si>
+  <si>
+    <t>BUDWISER MAGNUM STRONG BEER</t>
+  </si>
+  <si>
+    <t>CANNON 10000 BEER</t>
+  </si>
+  <si>
+    <t>CARLSBERG ELEPHANT STRONG BEER</t>
+  </si>
+  <si>
+    <t>HAYWARDS 2000 PREM. STRONG BEER</t>
+  </si>
+  <si>
+    <t>HAYWARDS 2000 ST. BEER</t>
+  </si>
+  <si>
+    <t>KING FISHER STR BEER</t>
+  </si>
+  <si>
+    <t>KING FISHER STR BOTLE</t>
+  </si>
+  <si>
+    <t>KINGFISHER SMOOTH STRONG PREMIUM BEER</t>
+  </si>
+  <si>
+    <t>MOUNT 6000 STRONG BEER</t>
+  </si>
+  <si>
+    <t>TUBORG CLASSIC STRONG BEER</t>
+  </si>
+  <si>
+    <t>BREEZER BLACKBERRY</t>
+  </si>
+  <si>
+    <t>BREEZER CRANBERRY</t>
+  </si>
+  <si>
+    <t>BUDWEISER KING OF BEER</t>
+  </si>
+  <si>
+    <t>CARLSBERG SMOOTH PREMIUM</t>
+  </si>
+  <si>
+    <t>KINGFISHER ULTRA LAGER BEER</t>
+  </si>
+  <si>
+    <t>MCD NO.1 RESERVE WHY. PET</t>
+  </si>
+  <si>
+    <t>Amber Whisky</t>
+  </si>
+  <si>
+    <t>BROWN MAN WHISKY</t>
+  </si>
+  <si>
+    <t>DERBY SPECIAL WHISKY</t>
+  </si>
+  <si>
+    <t>Gold Medal Rum</t>
+  </si>
+  <si>
+    <t>Gold Medal Vodka</t>
+  </si>
+  <si>
+    <t>MUMBAI MALT WHISKY</t>
+  </si>
+  <si>
+    <t>NAMASTE JAMUN VODKA</t>
+  </si>
+  <si>
+    <t>OLD ROYAL WHISKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAUS CRANBERRY VODKA </t>
+  </si>
+  <si>
+    <t>PAUS MANGO VODKA</t>
+  </si>
+  <si>
+    <t>RADICO NV GOA GIN MML</t>
+  </si>
+  <si>
+    <t>ROYAL SIGN WHISKY</t>
+  </si>
+  <si>
+    <t>RUSTOM GOLD RUM</t>
+  </si>
+  <si>
+    <t>SAHYADRI GOLD WHISKY</t>
+  </si>
+  <si>
+    <t>90(100)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -92,8 +370,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,88 +678,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>180</v>
       </c>
       <c r="C2">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>750</v>
       </c>
       <c r="C3">
-        <v>300</v>
+        <v>2800</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>750</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>3800</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>180</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>820</v>
       </c>
       <c r="D5">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>200</v>
       </c>
       <c r="C6">
         <v>800</v>
@@ -488,27 +773,27 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>750</v>
       </c>
       <c r="C7">
-        <v>400</v>
+        <v>2550</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>7</v>
+      <c r="B8">
+        <v>200</v>
       </c>
       <c r="C8">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -518,25 +803,25 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
+      <c r="B9">
+        <v>750</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>2400</v>
       </c>
       <c r="D9">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
+      <c r="B10">
+        <v>750</v>
       </c>
       <c r="C10">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="D10">
         <v>20</v>
@@ -544,54 +829,2677 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>750</v>
       </c>
       <c r="C11">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>90</v>
       </c>
       <c r="C12">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>180</v>
+      </c>
+      <c r="C13">
+        <v>220</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>375</v>
+      </c>
+      <c r="C14">
+        <v>440</v>
+      </c>
+      <c r="D14">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>750</v>
+      </c>
+      <c r="C15">
+        <v>880</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>90</v>
+      </c>
+      <c r="C16">
+        <v>140</v>
+      </c>
+      <c r="D16">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17">
+        <v>180</v>
+      </c>
+      <c r="C17">
+        <v>250</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>375</v>
+      </c>
+      <c r="C18">
+        <v>520</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>750</v>
+      </c>
+      <c r="C19">
+        <v>1070</v>
+      </c>
+      <c r="D19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20">
+        <v>180</v>
+      </c>
+      <c r="C20">
+        <v>430</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21">
+        <v>375</v>
+      </c>
+      <c r="C21">
+        <v>870</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <v>750</v>
+      </c>
+      <c r="C22">
+        <v>1740</v>
+      </c>
+      <c r="D22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>200</v>
+      </c>
+      <c r="C23">
+        <v>680</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>750</v>
+      </c>
+      <c r="C24">
+        <v>2500</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>180</v>
+      </c>
+      <c r="C25">
+        <v>730</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26">
+        <v>375</v>
+      </c>
+      <c r="C26">
+        <v>1500</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27">
+        <v>750</v>
+      </c>
+      <c r="C27">
+        <v>2900</v>
+      </c>
+      <c r="D27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>180</v>
+      </c>
+      <c r="C28">
+        <v>700</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>180</v>
+      </c>
+      <c r="C29">
+        <v>850</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>180</v>
+      </c>
+      <c r="C30">
+        <v>420</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
+        <v>375</v>
+      </c>
+      <c r="C31">
+        <v>840</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32">
+        <v>90</v>
+      </c>
+      <c r="C32">
+        <v>210</v>
+      </c>
+      <c r="D32">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33">
+        <v>180</v>
+      </c>
+      <c r="C33">
+        <v>400</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34">
+        <v>375</v>
+      </c>
+      <c r="C34">
+        <v>800</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35">
+        <v>750</v>
+      </c>
+      <c r="C35">
+        <v>1550</v>
+      </c>
+      <c r="D35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36">
+        <v>90</v>
+      </c>
+      <c r="C36">
+        <v>190</v>
+      </c>
+      <c r="D36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37">
+        <v>180</v>
+      </c>
+      <c r="C37">
+        <v>380</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38">
+        <v>375</v>
+      </c>
+      <c r="C38">
+        <v>760</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39">
+        <v>750</v>
+      </c>
+      <c r="C39">
+        <v>1500</v>
+      </c>
+      <c r="D39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40">
+        <v>1000</v>
+      </c>
+      <c r="C40">
+        <v>2000</v>
+      </c>
+      <c r="D40">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41">
+        <v>200</v>
+      </c>
+      <c r="C41">
+        <v>725</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42">
+        <v>200</v>
+      </c>
+      <c r="C42">
+        <v>600</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43">
+        <v>200</v>
+      </c>
+      <c r="C43">
+        <v>650</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44">
+        <v>200</v>
+      </c>
+      <c r="C44">
+        <v>1200</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45">
+        <v>2000</v>
+      </c>
+      <c r="C45">
+        <v>2200</v>
+      </c>
+      <c r="D45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46">
+        <v>110</v>
+      </c>
+      <c r="D46">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47">
+        <v>375</v>
+      </c>
+      <c r="C47">
+        <v>430</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48">
+        <v>750</v>
+      </c>
+      <c r="C48">
+        <v>860</v>
+      </c>
+      <c r="D48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49">
+        <v>1000</v>
+      </c>
+      <c r="C49">
+        <v>1150</v>
+      </c>
+      <c r="D49">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50">
+        <v>180</v>
+      </c>
+      <c r="C50">
+        <v>205</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51">
+        <v>200</v>
+      </c>
+      <c r="C51">
+        <v>850</v>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52">
+        <v>275</v>
+      </c>
+      <c r="C52">
+        <v>150</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53">
+        <v>90</v>
+      </c>
+      <c r="C53">
+        <v>150</v>
+      </c>
+      <c r="D53">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54">
+        <v>180</v>
+      </c>
+      <c r="C54">
+        <v>300</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55">
+        <v>750</v>
+      </c>
+      <c r="C55">
+        <v>1220</v>
+      </c>
+      <c r="D55">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56">
+        <v>90</v>
+      </c>
+      <c r="C56">
+        <v>150</v>
+      </c>
+      <c r="D56">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57">
+        <v>750</v>
+      </c>
+      <c r="C57">
+        <v>1220</v>
+      </c>
+      <c r="D57">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B58">
+        <v>180</v>
+      </c>
+      <c r="C58">
+        <v>300</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59">
+        <v>90</v>
+      </c>
+      <c r="C59">
+        <v>115</v>
+      </c>
+      <c r="D59">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60">
+        <v>180</v>
+      </c>
+      <c r="C60">
+        <v>220</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61">
+        <v>375</v>
+      </c>
+      <c r="C61">
+        <v>440</v>
+      </c>
+      <c r="D61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62">
+        <v>750</v>
+      </c>
+      <c r="C62">
+        <v>880</v>
+      </c>
+      <c r="D62">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63">
+        <v>120</v>
+      </c>
+      <c r="D63">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
+      </c>
+      <c r="C64">
+        <v>230</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65">
+        <v>375</v>
+      </c>
+      <c r="C65">
+        <v>460</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66">
+        <v>750</v>
+      </c>
+      <c r="C66">
+        <v>920</v>
+      </c>
+      <c r="D66">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67">
+        <v>2000</v>
+      </c>
+      <c r="C67">
+        <v>2300</v>
+      </c>
+      <c r="D67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>34</v>
+      </c>
+      <c r="B68">
+        <v>180</v>
+      </c>
+      <c r="C68">
+        <v>220</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>34</v>
+      </c>
+      <c r="B69">
+        <v>375</v>
+      </c>
+      <c r="C69">
+        <v>440</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70">
+        <v>750</v>
+      </c>
+      <c r="C70">
+        <v>880</v>
+      </c>
+      <c r="D70">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71">
+        <v>1000</v>
+      </c>
+      <c r="C71">
+        <v>1200</v>
+      </c>
+      <c r="D71">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72">
+        <v>2000</v>
+      </c>
+      <c r="C72">
+        <v>2400</v>
+      </c>
+      <c r="D72">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73">
+        <v>750</v>
+      </c>
+      <c r="C73">
+        <v>2300</v>
+      </c>
+      <c r="D73">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B74">
+        <v>750</v>
+      </c>
+      <c r="C74">
+        <v>4250</v>
+      </c>
+      <c r="D74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75">
+        <v>275</v>
+      </c>
+      <c r="C75">
+        <v>150</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76">
+        <v>375</v>
+      </c>
+      <c r="C76">
+        <v>1400</v>
+      </c>
+      <c r="D76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77">
+        <v>750</v>
+      </c>
+      <c r="C77">
+        <v>2500</v>
+      </c>
+      <c r="D77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78">
+        <v>750</v>
+      </c>
+      <c r="C78">
+        <v>3800</v>
+      </c>
+      <c r="D78">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B79">
+        <v>650</v>
+      </c>
+      <c r="C79">
+        <v>250</v>
+      </c>
+      <c r="D79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80">
+        <v>375</v>
+      </c>
+      <c r="C80">
+        <v>2100</v>
+      </c>
+      <c r="D80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81">
+        <v>750</v>
+      </c>
+      <c r="C81">
+        <v>3800</v>
+      </c>
+      <c r="D81">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82">
+        <v>750</v>
+      </c>
+      <c r="C82">
+        <v>3800</v>
+      </c>
+      <c r="D82">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83">
+        <v>750</v>
+      </c>
+      <c r="C83">
+        <v>3800</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84">
+        <v>650</v>
+      </c>
+      <c r="C84">
+        <v>260</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85">
+        <v>650</v>
+      </c>
+      <c r="C85">
+        <v>170</v>
+      </c>
+      <c r="D85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>43</v>
+      </c>
+      <c r="B86">
+        <v>90</v>
+      </c>
+      <c r="C86">
+        <v>145</v>
+      </c>
+      <c r="D86">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87">
+        <v>180</v>
+      </c>
+      <c r="C87">
+        <v>280</v>
+      </c>
+      <c r="D87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>43</v>
+      </c>
+      <c r="B88">
+        <v>375</v>
+      </c>
+      <c r="C88">
+        <v>560</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>43</v>
+      </c>
+      <c r="B89">
+        <v>750</v>
+      </c>
+      <c r="C89">
+        <v>1120</v>
+      </c>
+      <c r="D89">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>44</v>
+      </c>
+      <c r="B90">
+        <v>90</v>
+      </c>
+      <c r="C90">
+        <v>145</v>
+      </c>
+      <c r="D90">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B91">
+        <v>180</v>
+      </c>
+      <c r="C91">
+        <v>280</v>
+      </c>
+      <c r="D91">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92">
+        <v>375</v>
+      </c>
+      <c r="C92">
+        <v>560</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93">
+        <v>750</v>
+      </c>
+      <c r="C93">
+        <v>1120</v>
+      </c>
+      <c r="D93">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94">
+        <v>180</v>
+      </c>
+      <c r="C94">
+        <v>270</v>
+      </c>
+      <c r="D94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95">
+        <v>90</v>
+      </c>
+      <c r="C95">
+        <v>145</v>
+      </c>
+      <c r="D95">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>46</v>
+      </c>
+      <c r="B96">
+        <v>375</v>
+      </c>
+      <c r="C96">
+        <v>560</v>
+      </c>
+      <c r="D96">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>46</v>
+      </c>
+      <c r="B97">
+        <v>750</v>
+      </c>
+      <c r="C97">
+        <v>1120</v>
+      </c>
+      <c r="D97">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>47</v>
+      </c>
+      <c r="B98">
+        <v>90</v>
+      </c>
+      <c r="C98">
+        <v>145</v>
+      </c>
+      <c r="D98">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>47</v>
+      </c>
+      <c r="B99">
+        <v>180</v>
+      </c>
+      <c r="C99">
+        <v>280</v>
+      </c>
+      <c r="D99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>47</v>
+      </c>
+      <c r="B100">
+        <v>375</v>
+      </c>
+      <c r="C100">
+        <v>560</v>
+      </c>
+      <c r="D100">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>47</v>
+      </c>
+      <c r="B101">
+        <v>750</v>
+      </c>
+      <c r="C101">
+        <v>1120</v>
+      </c>
+      <c r="D101">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C102">
+        <v>105</v>
+      </c>
+      <c r="D102">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103">
+        <v>180</v>
+      </c>
+      <c r="C103">
+        <v>205</v>
+      </c>
+      <c r="D103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C104">
+        <v>120</v>
+      </c>
+      <c r="D104">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>85</v>
+      </c>
+      <c r="B105">
+        <v>180</v>
+      </c>
+      <c r="C105">
+        <v>210</v>
+      </c>
+      <c r="D105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>49</v>
+      </c>
+      <c r="B106">
+        <v>375</v>
+      </c>
+      <c r="C106">
+        <v>450</v>
+      </c>
+      <c r="D106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>49</v>
+      </c>
+      <c r="B107">
+        <v>750</v>
+      </c>
+      <c r="C107">
+        <v>900</v>
+      </c>
+      <c r="D107">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>49</v>
+      </c>
+      <c r="B108">
+        <v>1000</v>
+      </c>
+      <c r="C108">
+        <v>1200</v>
+      </c>
+      <c r="D108">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>49</v>
+      </c>
+      <c r="B109">
+        <v>2000</v>
+      </c>
+      <c r="C109">
+        <v>2400</v>
+      </c>
+      <c r="D109">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>50</v>
+      </c>
+      <c r="B110">
+        <v>180</v>
+      </c>
+      <c r="C110">
+        <v>400</v>
+      </c>
+      <c r="D110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>51</v>
+      </c>
+      <c r="B111">
+        <v>90</v>
+      </c>
+      <c r="C111">
+        <v>210</v>
+      </c>
+      <c r="D111">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>51</v>
+      </c>
+      <c r="B112">
+        <v>375</v>
+      </c>
+      <c r="C112">
+        <v>800</v>
+      </c>
+      <c r="D112">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>51</v>
+      </c>
+      <c r="B113">
+        <v>750</v>
+      </c>
+      <c r="C113">
+        <v>1600</v>
+      </c>
+      <c r="D113">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>52</v>
+      </c>
+      <c r="B114">
+        <v>180</v>
+      </c>
+      <c r="C114">
+        <v>330</v>
+      </c>
+      <c r="D114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>53</v>
+      </c>
+      <c r="B115">
+        <v>90</v>
+      </c>
+      <c r="C115">
+        <v>165</v>
+      </c>
+      <c r="D115">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>53</v>
+      </c>
+      <c r="B116">
+        <v>375</v>
+      </c>
+      <c r="C116">
+        <v>685</v>
+      </c>
+      <c r="D116">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>53</v>
+      </c>
+      <c r="B117">
+        <v>750</v>
+      </c>
+      <c r="C117">
+        <v>1370</v>
+      </c>
+      <c r="D117">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>54</v>
+      </c>
+      <c r="B118">
+        <v>180</v>
+      </c>
+      <c r="C118">
+        <v>220</v>
+      </c>
+      <c r="D118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>55</v>
+      </c>
+      <c r="B119">
+        <v>90</v>
+      </c>
+      <c r="C119">
+        <v>115</v>
+      </c>
+      <c r="D119">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120">
+        <v>180</v>
+      </c>
+      <c r="C120">
+        <v>220</v>
+      </c>
+      <c r="D120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>55</v>
+      </c>
+      <c r="B121">
+        <v>375</v>
+      </c>
+      <c r="C121">
+        <v>440</v>
+      </c>
+      <c r="D121">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>55</v>
+      </c>
+      <c r="B122">
+        <v>750</v>
+      </c>
+      <c r="C122">
+        <v>880</v>
+      </c>
+      <c r="D122">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>56</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C123">
+        <v>135</v>
+      </c>
+      <c r="D123">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124">
+        <v>375</v>
+      </c>
+      <c r="C124">
+        <v>520</v>
+      </c>
+      <c r="D124">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>56</v>
+      </c>
+      <c r="B125">
+        <v>750</v>
+      </c>
+      <c r="C125">
+        <v>1070</v>
+      </c>
+      <c r="D125">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>56</v>
+      </c>
+      <c r="B126">
+        <v>1000</v>
+      </c>
+      <c r="C126">
+        <v>1400</v>
+      </c>
+      <c r="D126">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>56</v>
+      </c>
+      <c r="B127">
+        <v>2000</v>
+      </c>
+      <c r="C127">
+        <v>2800</v>
+      </c>
+      <c r="D127">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>57</v>
+      </c>
+      <c r="B128">
+        <v>180</v>
+      </c>
+      <c r="C128">
+        <v>250</v>
+      </c>
+      <c r="D128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>58</v>
+      </c>
+      <c r="B129">
+        <v>90</v>
+      </c>
+      <c r="C129">
+        <v>140</v>
+      </c>
+      <c r="D129">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>58</v>
+      </c>
+      <c r="B130">
+        <v>180</v>
+      </c>
+      <c r="C130">
+        <v>260</v>
+      </c>
+      <c r="D130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>58</v>
+      </c>
+      <c r="B131">
+        <v>375</v>
+      </c>
+      <c r="C131">
+        <v>550</v>
+      </c>
+      <c r="D131">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>58</v>
+      </c>
+      <c r="B132">
+        <v>750</v>
+      </c>
+      <c r="C132">
+        <v>1100</v>
+      </c>
+      <c r="D132">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>58</v>
+      </c>
+      <c r="B133">
+        <v>1000</v>
+      </c>
+      <c r="C133">
+        <v>1450</v>
+      </c>
+      <c r="D133">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>58</v>
+      </c>
+      <c r="B134">
+        <v>2000</v>
+      </c>
+      <c r="C134">
+        <v>2800</v>
+      </c>
+      <c r="D134">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>59</v>
+      </c>
+      <c r="B135">
+        <v>180</v>
+      </c>
+      <c r="C135">
+        <v>725</v>
+      </c>
+      <c r="D135">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>59</v>
+      </c>
+      <c r="B136">
+        <v>375</v>
+      </c>
+      <c r="C136">
+        <v>1400</v>
+      </c>
+      <c r="D136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>59</v>
+      </c>
+      <c r="B137">
+        <v>750</v>
+      </c>
+      <c r="C137">
+        <v>2800</v>
+      </c>
+      <c r="D137">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>60</v>
+      </c>
+      <c r="B138">
+        <v>375</v>
+      </c>
+      <c r="C138">
+        <v>560</v>
+      </c>
+      <c r="D138">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>60</v>
+      </c>
+      <c r="B139">
+        <v>750</v>
+      </c>
+      <c r="C139">
+        <v>1200</v>
+      </c>
+      <c r="D139">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>61</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C140">
+        <v>140</v>
+      </c>
+      <c r="D140">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>61</v>
+      </c>
+      <c r="B141">
+        <v>180</v>
+      </c>
+      <c r="C141">
+        <v>250</v>
+      </c>
+      <c r="D141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>61</v>
+      </c>
+      <c r="B142">
+        <v>375</v>
+      </c>
+      <c r="C142">
+        <v>520</v>
+      </c>
+      <c r="D142">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>61</v>
+      </c>
+      <c r="B143">
+        <v>750</v>
+      </c>
+      <c r="C143">
+        <v>1070</v>
+      </c>
+      <c r="D143">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>61</v>
+      </c>
+      <c r="B144">
+        <v>1000</v>
+      </c>
+      <c r="C144">
+        <v>1400</v>
+      </c>
+      <c r="D144">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>61</v>
+      </c>
+      <c r="B145">
+        <v>2000</v>
+      </c>
+      <c r="C145">
+        <v>2800</v>
+      </c>
+      <c r="D145">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>62</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C146">
+        <v>170</v>
+      </c>
+      <c r="D146">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>62</v>
+      </c>
+      <c r="B147">
+        <v>180</v>
+      </c>
+      <c r="C147">
+        <v>320</v>
+      </c>
+      <c r="D147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>62</v>
+      </c>
+      <c r="B148">
+        <v>375</v>
+      </c>
+      <c r="C148">
+        <v>640</v>
+      </c>
+      <c r="D148">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>62</v>
+      </c>
+      <c r="B149">
+        <v>750</v>
+      </c>
+      <c r="C149">
+        <v>1280</v>
+      </c>
+      <c r="D149">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>63</v>
+      </c>
+      <c r="B150">
+        <v>180</v>
+      </c>
+      <c r="C150">
+        <v>440</v>
+      </c>
+      <c r="D150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>64</v>
+      </c>
+      <c r="B151">
+        <v>180</v>
+      </c>
+      <c r="C151">
+        <v>440</v>
+      </c>
+      <c r="D151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>65</v>
+      </c>
+      <c r="B152">
+        <v>180</v>
+      </c>
+      <c r="C152">
+        <v>440</v>
+      </c>
+      <c r="D152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>66</v>
+      </c>
+      <c r="B153">
+        <v>180</v>
+      </c>
+      <c r="C153">
+        <v>425</v>
+      </c>
+      <c r="D153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>67</v>
+      </c>
+      <c r="B154">
+        <v>180</v>
+      </c>
+      <c r="C154">
+        <v>440</v>
+      </c>
+      <c r="D154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>68</v>
+      </c>
+      <c r="B155">
+        <v>90</v>
+      </c>
+      <c r="C155">
+        <v>135</v>
+      </c>
+      <c r="D155">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>68</v>
+      </c>
+      <c r="B156">
+        <v>180</v>
+      </c>
+      <c r="C156">
+        <v>250</v>
+      </c>
+      <c r="D156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>68</v>
+      </c>
+      <c r="B157">
+        <v>375</v>
+      </c>
+      <c r="C157">
+        <v>520</v>
+      </c>
+      <c r="D157">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>73</v>
+      </c>
+      <c r="B158">
+        <v>650</v>
+      </c>
+      <c r="C158">
+        <v>160</v>
+      </c>
+      <c r="D158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>70</v>
+      </c>
+      <c r="B159">
+        <v>500</v>
+      </c>
+      <c r="C159">
+        <v>200</v>
+      </c>
+      <c r="D159">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>75</v>
+      </c>
+      <c r="B160">
+        <v>650</v>
+      </c>
+      <c r="C160">
+        <v>200</v>
+      </c>
+      <c r="D160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>71</v>
+      </c>
+      <c r="B161">
+        <v>330</v>
+      </c>
+      <c r="C161">
+        <v>95</v>
+      </c>
+      <c r="D161">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>79</v>
+      </c>
+      <c r="B162">
+        <v>650</v>
+      </c>
+      <c r="C162">
+        <v>240</v>
+      </c>
+      <c r="D162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>72</v>
+      </c>
+      <c r="B163">
+        <v>500</v>
+      </c>
+      <c r="C163">
+        <v>200</v>
+      </c>
+      <c r="D163">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>82</v>
+      </c>
+      <c r="B164">
+        <v>650</v>
+      </c>
+      <c r="C164">
+        <v>245</v>
+      </c>
+      <c r="D164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>74</v>
+      </c>
+      <c r="B165">
+        <v>500</v>
+      </c>
+      <c r="C165">
+        <v>120</v>
+      </c>
+      <c r="D165">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>83</v>
+      </c>
+      <c r="B166">
+        <v>650</v>
+      </c>
+      <c r="C166">
+        <v>240</v>
+      </c>
+      <c r="D166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>76</v>
+      </c>
+      <c r="B167">
+        <v>330</v>
+      </c>
+      <c r="C167">
+        <v>135</v>
+      </c>
+      <c r="D167">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>77</v>
+      </c>
+      <c r="B168">
+        <v>500</v>
+      </c>
+      <c r="C168">
+        <v>155</v>
+      </c>
+      <c r="D168">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>78</v>
+      </c>
+      <c r="B169">
+        <v>500</v>
+      </c>
+      <c r="C169">
+        <v>120</v>
+      </c>
+      <c r="D169">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>84</v>
+      </c>
+      <c r="B170">
+        <v>650</v>
+      </c>
+      <c r="C170">
+        <v>220</v>
+      </c>
+      <c r="D170">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>22</v>
+      </c>
+      <c r="B171">
+        <v>700</v>
+      </c>
+      <c r="C171">
+        <v>2500</v>
+      </c>
+      <c r="D171">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>23</v>
+      </c>
+      <c r="B172">
+        <v>700</v>
+      </c>
+      <c r="C172">
+        <v>1800</v>
+      </c>
+      <c r="D172">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>82</v>
+      </c>
+      <c r="B173">
+        <v>500</v>
+      </c>
+      <c r="C173">
+        <v>190</v>
+      </c>
+      <c r="D173">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>27</v>
+      </c>
+      <c r="B174">
+        <v>700</v>
+      </c>
+      <c r="C174">
+        <v>2300</v>
+      </c>
+      <c r="D174">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>28</v>
+      </c>
+      <c r="B175">
+        <v>700</v>
+      </c>
+      <c r="C175">
+        <v>1900</v>
+      </c>
+      <c r="D175">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>42</v>
+      </c>
+      <c r="B176">
+        <v>700</v>
+      </c>
+      <c r="C176">
+        <v>3200</v>
+      </c>
+      <c r="D176">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C177">
+        <v>75</v>
+      </c>
+      <c r="D177">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>88</v>
+      </c>
+      <c r="B178">
+        <v>90</v>
+      </c>
+      <c r="C178">
+        <v>80</v>
+      </c>
+      <c r="D178">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>89</v>
+      </c>
+      <c r="B179">
+        <v>90</v>
+      </c>
+      <c r="C179">
+        <v>75</v>
+      </c>
+      <c r="D179">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>98</v>
+      </c>
+      <c r="B180">
+        <v>90</v>
+      </c>
+      <c r="C180">
+        <v>75</v>
+      </c>
+      <c r="D180">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>86</v>
+      </c>
+      <c r="B181">
+        <v>180</v>
+      </c>
+      <c r="C181">
+        <v>150</v>
+      </c>
+      <c r="D181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>87</v>
+      </c>
+      <c r="B182">
+        <v>180</v>
+      </c>
+      <c r="C182">
+        <v>150</v>
+      </c>
+      <c r="D182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>88</v>
+      </c>
+      <c r="B183">
+        <v>180</v>
+      </c>
+      <c r="C183">
+        <v>160</v>
+      </c>
+      <c r="D183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>89</v>
+      </c>
+      <c r="B184">
+        <v>180</v>
+      </c>
+      <c r="C184">
+        <v>150</v>
+      </c>
+      <c r="D184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>91</v>
+      </c>
+      <c r="B185">
+        <v>180</v>
+      </c>
+      <c r="C185">
+        <v>150</v>
+      </c>
+      <c r="D185">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>92</v>
+      </c>
+      <c r="B186">
+        <v>180</v>
+      </c>
+      <c r="C186">
+        <v>180</v>
+      </c>
+      <c r="D186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>93</v>
+      </c>
+      <c r="B187">
+        <v>180</v>
+      </c>
+      <c r="C187">
+        <v>180</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>94</v>
+      </c>
+      <c r="B188">
+        <v>180</v>
+      </c>
+      <c r="C188">
+        <v>170</v>
+      </c>
+      <c r="D188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>95</v>
+      </c>
+      <c r="B189">
+        <v>180</v>
+      </c>
+      <c r="C189">
+        <v>170</v>
+      </c>
+      <c r="D189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>96</v>
+      </c>
+      <c r="B190">
+        <v>180</v>
+      </c>
+      <c r="C190">
         <v>130</v>
       </c>
-      <c r="D13">
-        <v>2.5</v>
+      <c r="D190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>97</v>
+      </c>
+      <c r="B191">
+        <v>180</v>
+      </c>
+      <c r="C191">
+        <v>150</v>
+      </c>
+      <c r="D191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>98</v>
+      </c>
+      <c r="B192">
+        <v>180</v>
+      </c>
+      <c r="C192">
+        <v>150</v>
+      </c>
+      <c r="D192">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>99</v>
+      </c>
+      <c r="B193">
+        <v>180</v>
+      </c>
+      <c r="C193">
+        <v>180</v>
+      </c>
+      <c r="D193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>86</v>
+      </c>
+      <c r="B194">
+        <v>750</v>
+      </c>
+      <c r="C194">
+        <v>620</v>
+      </c>
+      <c r="D194">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>88</v>
+      </c>
+      <c r="B195">
+        <v>750</v>
+      </c>
+      <c r="C195">
+        <v>660</v>
+      </c>
+      <c r="D195">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>89</v>
+      </c>
+      <c r="B196">
+        <v>750</v>
+      </c>
+      <c r="C196">
+        <v>620</v>
+      </c>
+      <c r="D196">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>90</v>
+      </c>
+      <c r="B197">
+        <v>750</v>
+      </c>
+      <c r="C197">
+        <v>620</v>
+      </c>
+      <c r="D197">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>93</v>
+      </c>
+      <c r="B198">
+        <v>750</v>
+      </c>
+      <c r="C198">
+        <v>700</v>
+      </c>
+      <c r="D198">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>98</v>
+      </c>
+      <c r="B199">
+        <v>750</v>
+      </c>
+      <c r="C199">
+        <v>600</v>
+      </c>
+      <c r="D199">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>99</v>
+      </c>
+      <c r="B200">
+        <v>750</v>
+      </c>
+      <c r="C200">
+        <v>720</v>
+      </c>
+      <c r="D200">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D200" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A177:D200">
+      <sortCondition ref="B1:B200"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435BA7B5-0C86-49DF-B086-151D34E3E6C4}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -602,42 +3510,117 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
+      <c r="A2">
+        <v>2000</v>
       </c>
       <c r="B2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1000</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>750</v>
+      </c>
+      <c r="B4">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>700</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>650</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>500</v>
+      </c>
+      <c r="B7">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>375</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>330</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>275</v>
+      </c>
+      <c r="B10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>200</v>
+      </c>
+      <c r="B11">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>180</v>
+      </c>
+      <c r="B12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>90</v>
+      </c>
+      <c r="B13">
         <v>96</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B13">
+    <sortCondition descending="1" ref="A2:A13"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/items_data.xlsx
+++ b/items_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BillCalculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BillCalculator\BillCalculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63139AF-3A66-4F97-9228-F3DF8FF82E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C0B14C-2299-4622-A031-BAFB9FDA70F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="BoxSize" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$D$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$D$201</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="102">
   <si>
     <t>Item Name</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>90(100)</t>
+  </si>
+  <si>
+    <t>GRAND MASTER Mango VODKA</t>
   </si>
 </sst>
 </file>
@@ -678,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.28515625" bestFit="1" customWidth="1"/>
@@ -1487,7 +1490,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="B58">
         <v>180</v>
@@ -1501,16 +1504,16 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B59">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C59">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="D59">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,13 +1521,13 @@
         <v>32</v>
       </c>
       <c r="B60">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C60">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1532,13 +1535,13 @@
         <v>32</v>
       </c>
       <c r="B61">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C61">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,41 +1549,41 @@
         <v>32</v>
       </c>
       <c r="B62">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C62">
-        <v>880</v>
+        <v>440</v>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>33</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>100</v>
+        <v>32</v>
+      </c>
+      <c r="B63">
+        <v>750</v>
       </c>
       <c r="C63">
-        <v>120</v>
+        <v>880</v>
       </c>
       <c r="D63">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>33</v>
       </c>
-      <c r="B64">
-        <v>180</v>
+      <c r="B64" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C64">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,13 +1591,13 @@
         <v>33</v>
       </c>
       <c r="B65">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C65">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,13 +1605,13 @@
         <v>33</v>
       </c>
       <c r="B66">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C66">
-        <v>920</v>
+        <v>460</v>
       </c>
       <c r="D66">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,27 +1619,27 @@
         <v>33</v>
       </c>
       <c r="B67">
-        <v>2000</v>
+        <v>750</v>
       </c>
       <c r="C67">
-        <v>2300</v>
+        <v>920</v>
       </c>
       <c r="D67">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68">
-        <v>180</v>
+        <v>2000</v>
       </c>
       <c r="C68">
-        <v>220</v>
+        <v>2300</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,13 +1647,13 @@
         <v>34</v>
       </c>
       <c r="B69">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C69">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1658,13 +1661,13 @@
         <v>34</v>
       </c>
       <c r="B70">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C70">
-        <v>880</v>
+        <v>440</v>
       </c>
       <c r="D70">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1672,13 +1675,13 @@
         <v>34</v>
       </c>
       <c r="B71">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C71">
-        <v>1200</v>
+        <v>880</v>
       </c>
       <c r="D71">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,38 +1689,38 @@
         <v>34</v>
       </c>
       <c r="B72">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C72">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="D72">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B73">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="C73">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B74">
         <v>750</v>
       </c>
       <c r="C74">
-        <v>4250</v>
+        <v>2300</v>
       </c>
       <c r="D74">
         <v>20</v>
@@ -1725,30 +1728,30 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="B75">
-        <v>275</v>
+        <v>750</v>
       </c>
       <c r="C75">
-        <v>150</v>
+        <v>4250</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="B76">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="C76">
-        <v>1400</v>
+        <v>150</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1756,24 +1759,24 @@
         <v>37</v>
       </c>
       <c r="B77">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C77">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B78">
         <v>750</v>
       </c>
       <c r="C78">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="D78">
         <v>20</v>
@@ -1781,30 +1784,30 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B79">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="C79">
-        <v>250</v>
+        <v>3800</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B80">
-        <v>375</v>
+        <v>650</v>
       </c>
       <c r="C80">
-        <v>2100</v>
+        <v>250</v>
       </c>
       <c r="D80">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,18 +1815,18 @@
         <v>39</v>
       </c>
       <c r="B81">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C81">
-        <v>3800</v>
+        <v>2100</v>
       </c>
       <c r="D81">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B82">
         <v>750</v>
@@ -1837,7 +1840,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B83">
         <v>750</v>
@@ -1851,27 +1854,27 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B84">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="C84">
-        <v>260</v>
+        <v>3800</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B85">
         <v>650</v>
       </c>
       <c r="C85">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -1879,16 +1882,16 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B86">
-        <v>90</v>
+        <v>650</v>
       </c>
       <c r="C86">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D86">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,13 +1899,13 @@
         <v>43</v>
       </c>
       <c r="B87">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C87">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -1910,13 +1913,13 @@
         <v>43</v>
       </c>
       <c r="B88">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C88">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -1924,27 +1927,27 @@
         <v>43</v>
       </c>
       <c r="B89">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C89">
-        <v>1120</v>
+        <v>560</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B90">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="C90">
-        <v>145</v>
+        <v>1120</v>
       </c>
       <c r="D90">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -1952,13 +1955,13 @@
         <v>44</v>
       </c>
       <c r="B91">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C91">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -1966,13 +1969,13 @@
         <v>44</v>
       </c>
       <c r="B92">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C92">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -1980,41 +1983,41 @@
         <v>44</v>
       </c>
       <c r="B93">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C93">
-        <v>1120</v>
+        <v>560</v>
       </c>
       <c r="D93">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B94">
-        <v>180</v>
+        <v>750</v>
       </c>
       <c r="C94">
-        <v>270</v>
+        <v>1120</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B95">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C95">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="D95">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2022,13 +2025,13 @@
         <v>46</v>
       </c>
       <c r="B96">
-        <v>375</v>
+        <v>90</v>
       </c>
       <c r="C96">
-        <v>560</v>
+        <v>145</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2036,27 +2039,27 @@
         <v>46</v>
       </c>
       <c r="B97">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C97">
-        <v>1120</v>
+        <v>560</v>
       </c>
       <c r="D97">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B98">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="C98">
-        <v>145</v>
+        <v>1120</v>
       </c>
       <c r="D98">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2064,13 +2067,13 @@
         <v>47</v>
       </c>
       <c r="B99">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C99">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2078,13 +2081,13 @@
         <v>47</v>
       </c>
       <c r="B100">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C100">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,83 +2095,83 @@
         <v>47</v>
       </c>
       <c r="B101">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C101">
-        <v>1120</v>
+        <v>560</v>
       </c>
       <c r="D101">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>48</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="B102">
+        <v>750</v>
       </c>
       <c r="C102">
-        <v>105</v>
+        <v>1120</v>
       </c>
       <c r="D102">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>48</v>
       </c>
-      <c r="B103">
-        <v>180</v>
+      <c r="B103" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C103">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>49</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>100</v>
+        <v>48</v>
+      </c>
+      <c r="B104">
+        <v>180</v>
       </c>
       <c r="C104">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="D104">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>85</v>
-      </c>
-      <c r="B105">
-        <v>180</v>
+        <v>49</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C105">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B106">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C106">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="D106">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2176,13 +2179,13 @@
         <v>49</v>
       </c>
       <c r="B107">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C107">
-        <v>900</v>
+        <v>450</v>
       </c>
       <c r="D107">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -2190,13 +2193,13 @@
         <v>49</v>
       </c>
       <c r="B108">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C108">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="D108">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -2204,41 +2207,41 @@
         <v>49</v>
       </c>
       <c r="B109">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C109">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="D109">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>49</v>
+      </c>
+      <c r="B110">
+        <v>2000</v>
+      </c>
+      <c r="C110">
+        <v>2400</v>
+      </c>
+      <c r="D110">
         <v>50</v>
-      </c>
-      <c r="B110">
-        <v>180</v>
-      </c>
-      <c r="C110">
-        <v>400</v>
-      </c>
-      <c r="D110">
-        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B111">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C111">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="D111">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -2246,13 +2249,13 @@
         <v>51</v>
       </c>
       <c r="B112">
-        <v>375</v>
+        <v>90</v>
       </c>
       <c r="C112">
-        <v>800</v>
+        <v>210</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -2260,41 +2263,41 @@
         <v>51</v>
       </c>
       <c r="B113">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C113">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="D113">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B114">
-        <v>180</v>
+        <v>750</v>
       </c>
       <c r="C114">
-        <v>330</v>
+        <v>1600</v>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B115">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C115">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="D115">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,13 +2305,13 @@
         <v>53</v>
       </c>
       <c r="B116">
-        <v>375</v>
+        <v>90</v>
       </c>
       <c r="C116">
-        <v>685</v>
+        <v>165</v>
       </c>
       <c r="D116">
-        <v>10</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -2316,41 +2319,41 @@
         <v>53</v>
       </c>
       <c r="B117">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C117">
-        <v>1370</v>
+        <v>685</v>
       </c>
       <c r="D117">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B118">
-        <v>180</v>
+        <v>750</v>
       </c>
       <c r="C118">
-        <v>220</v>
+        <v>1370</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B119">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C119">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="D119">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -2358,13 +2361,13 @@
         <v>55</v>
       </c>
       <c r="B120">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C120">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -2372,13 +2375,13 @@
         <v>55</v>
       </c>
       <c r="B121">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C121">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="D121">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -2386,41 +2389,41 @@
         <v>55</v>
       </c>
       <c r="B122">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C122">
-        <v>880</v>
+        <v>440</v>
       </c>
       <c r="D122">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>56</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>100</v>
+        <v>55</v>
+      </c>
+      <c r="B123">
+        <v>750</v>
       </c>
       <c r="C123">
-        <v>135</v>
+        <v>880</v>
       </c>
       <c r="D123">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>56</v>
       </c>
-      <c r="B124">
-        <v>375</v>
+      <c r="B124" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C124">
-        <v>520</v>
+        <v>135</v>
       </c>
       <c r="D124">
-        <v>10</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -2428,13 +2431,13 @@
         <v>56</v>
       </c>
       <c r="B125">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C125">
-        <v>1070</v>
+        <v>520</v>
       </c>
       <c r="D125">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -2442,13 +2445,13 @@
         <v>56</v>
       </c>
       <c r="B126">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C126">
-        <v>1400</v>
+        <v>1070</v>
       </c>
       <c r="D126">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -2456,41 +2459,41 @@
         <v>56</v>
       </c>
       <c r="B127">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C127">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="D127">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B128">
-        <v>180</v>
+        <v>2000</v>
       </c>
       <c r="C128">
-        <v>250</v>
+        <v>2800</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B129">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C129">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="D129">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -2498,13 +2501,13 @@
         <v>58</v>
       </c>
       <c r="B130">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C130">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -2512,13 +2515,13 @@
         <v>58</v>
       </c>
       <c r="B131">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C131">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="D131">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -2526,13 +2529,13 @@
         <v>58</v>
       </c>
       <c r="B132">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C132">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="D132">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -2540,13 +2543,13 @@
         <v>58</v>
       </c>
       <c r="B133">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C133">
-        <v>1450</v>
+        <v>1100</v>
       </c>
       <c r="D133">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -2554,27 +2557,27 @@
         <v>58</v>
       </c>
       <c r="B134">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C134">
-        <v>2800</v>
+        <v>1450</v>
       </c>
       <c r="D134">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B135">
-        <v>180</v>
+        <v>2000</v>
       </c>
       <c r="C135">
-        <v>725</v>
+        <v>2800</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -2582,13 +2585,13 @@
         <v>59</v>
       </c>
       <c r="B136">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C136">
-        <v>1400</v>
+        <v>725</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -2596,27 +2599,27 @@
         <v>59</v>
       </c>
       <c r="B137">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C137">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="D137">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B138">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="C138">
-        <v>560</v>
+        <v>2800</v>
       </c>
       <c r="D138">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -2624,41 +2627,41 @@
         <v>60</v>
       </c>
       <c r="B139">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C139">
-        <v>1200</v>
+        <v>560</v>
       </c>
       <c r="D139">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>61</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="B140">
+        <v>750</v>
       </c>
       <c r="C140">
-        <v>140</v>
+        <v>1200</v>
       </c>
       <c r="D140">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>61</v>
       </c>
-      <c r="B141">
-        <v>180</v>
+      <c r="B141" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C141">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -2666,13 +2669,13 @@
         <v>61</v>
       </c>
       <c r="B142">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C142">
-        <v>520</v>
+        <v>250</v>
       </c>
       <c r="D142">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -2680,13 +2683,13 @@
         <v>61</v>
       </c>
       <c r="B143">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C143">
-        <v>1070</v>
+        <v>520</v>
       </c>
       <c r="D143">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,13 +2697,13 @@
         <v>61</v>
       </c>
       <c r="B144">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C144">
-        <v>1400</v>
+        <v>1070</v>
       </c>
       <c r="D144">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -2708,41 +2711,41 @@
         <v>61</v>
       </c>
       <c r="B145">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C145">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="D145">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>62</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>100</v>
+        <v>61</v>
+      </c>
+      <c r="B146">
+        <v>2000</v>
       </c>
       <c r="C146">
-        <v>170</v>
+        <v>2800</v>
       </c>
       <c r="D146">
-        <v>2.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>62</v>
       </c>
-      <c r="B147">
-        <v>180</v>
+      <c r="B147" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C147">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -2750,13 +2753,13 @@
         <v>62</v>
       </c>
       <c r="B148">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C148">
-        <v>640</v>
+        <v>320</v>
       </c>
       <c r="D148">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -2764,32 +2767,32 @@
         <v>62</v>
       </c>
       <c r="B149">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C149">
-        <v>1280</v>
+        <v>640</v>
       </c>
       <c r="D149">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B150">
-        <v>180</v>
+        <v>750</v>
       </c>
       <c r="C150">
-        <v>440</v>
+        <v>1280</v>
       </c>
       <c r="D150">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B151">
         <v>180</v>
@@ -2803,7 +2806,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B152">
         <v>180</v>
@@ -2817,13 +2820,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B153">
         <v>180</v>
       </c>
       <c r="C153">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="D153">
         <v>5</v>
@@ -2831,13 +2834,13 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B154">
         <v>180</v>
       </c>
       <c r="C154">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="D154">
         <v>5</v>
@@ -2845,16 +2848,16 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B155">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C155">
-        <v>135</v>
+        <v>440</v>
       </c>
       <c r="D155">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -2862,13 +2865,13 @@
         <v>68</v>
       </c>
       <c r="B156">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C156">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -2876,164 +2879,164 @@
         <v>68</v>
       </c>
       <c r="B157">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="C157">
-        <v>520</v>
+        <v>250</v>
       </c>
       <c r="D157">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B158">
-        <v>650</v>
+        <v>375</v>
       </c>
       <c r="C158">
-        <v>160</v>
+        <v>520</v>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B159">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="C159">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D159">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B160">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="C160">
         <v>200</v>
       </c>
       <c r="D160">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B161">
-        <v>330</v>
+        <v>650</v>
       </c>
       <c r="C161">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="D161">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B162">
-        <v>650</v>
+        <v>330</v>
       </c>
       <c r="C162">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="D162">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B163">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="C163">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="D163">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B164">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="C164">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B165">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="C165">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="D165">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B166">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="C166">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B167">
-        <v>330</v>
+        <v>650</v>
       </c>
       <c r="C167">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="D167">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B168">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="C168">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="D168">
         <v>2.5</v>
@@ -3041,13 +3044,13 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B169">
         <v>500</v>
       </c>
       <c r="C169">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="D169">
         <v>2.5</v>
@@ -3055,41 +3058,41 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B170">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="C170">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="B171">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="C171">
-        <v>2500</v>
+        <v>220</v>
       </c>
       <c r="D171">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B172">
         <v>700</v>
       </c>
       <c r="C172">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="D172">
         <v>20</v>
@@ -3097,41 +3100,41 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="B173">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C173">
-        <v>190</v>
+        <v>1800</v>
       </c>
       <c r="D173">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="B174">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C174">
-        <v>2300</v>
+        <v>190</v>
       </c>
       <c r="D174">
-        <v>20</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B175">
         <v>700</v>
       </c>
       <c r="C175">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="D175">
         <v>20</v>
@@ -3139,13 +3142,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B176">
         <v>700</v>
       </c>
       <c r="C176">
-        <v>3200</v>
+        <v>1900</v>
       </c>
       <c r="D176">
         <v>20</v>
@@ -3153,27 +3156,27 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>87</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>100</v>
+        <v>42</v>
+      </c>
+      <c r="B177">
+        <v>700</v>
       </c>
       <c r="C177">
-        <v>75</v>
+        <v>3200</v>
       </c>
       <c r="D177">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>88</v>
-      </c>
-      <c r="B178">
-        <v>90</v>
+        <v>87</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C178">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D178">
         <v>2.5</v>
@@ -3181,13 +3184,13 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B179">
         <v>90</v>
       </c>
       <c r="C179">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D179">
         <v>2.5</v>
@@ -3195,7 +3198,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B180">
         <v>90</v>
@@ -3209,21 +3212,21 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B181">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C181">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B182">
         <v>180</v>
@@ -3237,13 +3240,13 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B183">
         <v>180</v>
       </c>
       <c r="C183">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D183">
         <v>5</v>
@@ -3251,13 +3254,13 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B184">
         <v>180</v>
       </c>
       <c r="C184">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D184">
         <v>5</v>
@@ -3265,7 +3268,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B185">
         <v>180</v>
@@ -3279,13 +3282,13 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B186">
         <v>180</v>
       </c>
       <c r="C186">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D186">
         <v>5</v>
@@ -3293,7 +3296,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B187">
         <v>180</v>
@@ -3307,13 +3310,13 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B188">
         <v>180</v>
       </c>
       <c r="C188">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D188">
         <v>5</v>
@@ -3321,7 +3324,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B189">
         <v>180</v>
@@ -3335,13 +3338,13 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B190">
         <v>180</v>
       </c>
       <c r="C190">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D190">
         <v>5</v>
@@ -3349,13 +3352,13 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B191">
         <v>180</v>
       </c>
       <c r="C191">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D191">
         <v>5</v>
@@ -3363,7 +3366,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B192">
         <v>180</v>
@@ -3377,13 +3380,13 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B193">
         <v>180</v>
       </c>
       <c r="C193">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D193">
         <v>5</v>
@@ -3391,27 +3394,27 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B194">
-        <v>750</v>
+        <v>180</v>
       </c>
       <c r="C194">
-        <v>620</v>
+        <v>180</v>
       </c>
       <c r="D194">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B195">
         <v>750</v>
       </c>
       <c r="C195">
-        <v>660</v>
+        <v>620</v>
       </c>
       <c r="D195">
         <v>20</v>
@@ -3419,13 +3422,13 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B196">
         <v>750</v>
       </c>
       <c r="C196">
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="D196">
         <v>20</v>
@@ -3433,7 +3436,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B197">
         <v>750</v>
@@ -3447,13 +3450,13 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B198">
         <v>750</v>
       </c>
       <c r="C198">
-        <v>700</v>
+        <v>620</v>
       </c>
       <c r="D198">
         <v>20</v>
@@ -3461,13 +3464,13 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B199">
         <v>750</v>
       </c>
       <c r="C199">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D199">
         <v>20</v>
@@ -3475,22 +3478,36 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>98</v>
+      </c>
+      <c r="B200">
+        <v>750</v>
+      </c>
+      <c r="C200">
+        <v>600</v>
+      </c>
+      <c r="D200">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
         <v>99</v>
       </c>
-      <c r="B200">
-        <v>750</v>
-      </c>
-      <c r="C200">
+      <c r="B201">
+        <v>750</v>
+      </c>
+      <c r="C201">
         <v>720</v>
       </c>
-      <c r="D200">
+      <c r="D201">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D200" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A177:D200">
-      <sortCondition ref="B1:B200"/>
+  <autoFilter ref="A1:D201" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A178:D201">
+      <sortCondition ref="B1:B201"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
